--- a/Canciones para Dios Word/Canciones_Dios_Lista_canciones.xlsx
+++ b/Canciones para Dios Word/Canciones_Dios_Lista_canciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterDev\Canciones para Dios Word\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E227FD3-113F-49F1-81C2-0A90E080A00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DBE486-47A7-420D-8E6D-428403A42F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="148">
   <si>
     <t>A edificar la iglesia</t>
   </si>
@@ -272,9 +272,6 @@
     <t>https://www.youtube.com/results?search_query=El+Se%C3%B1or+es+mi+Pastor+canto</t>
   </si>
   <si>
-    <t>Misericordia Señor</t>
-  </si>
-  <si>
     <t>Penitencial</t>
   </si>
   <si>
@@ -480,6 +477,9 @@
   </si>
   <si>
     <t>Ven Señor a nuestra vida</t>
+  </si>
+  <si>
+    <t>Misericordia Señor por tu Bondad</t>
   </si>
 </sst>
 </file>
@@ -509,7 +509,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,6 +519,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -535,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -550,6 +556,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -897,7 +904,7 @@
         <v>10048</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" t="str">
         <f>"'"&amp;B4&amp;A4&amp;"'"&amp;","</f>
@@ -993,7 +1000,7 @@
         <v>10050</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10" t="str">
         <f>"'"&amp;B10&amp;A10&amp;"'"&amp;","</f>
@@ -1202,7 +1209,7 @@
         <v>10052</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" t="str">
         <f>"'"&amp;B23&amp;A23&amp;"'"&amp;","</f>
@@ -1266,7 +1273,7 @@
         <v>10053</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C27" t="str">
         <f>"'"&amp;B27&amp;A27&amp;"'"&amp;","</f>
@@ -1314,7 +1321,7 @@
         <v>10054</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C30" t="str">
         <f>"'"&amp;B30&amp;A30&amp;"'"&amp;","</f>
@@ -1359,415 +1366,418 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>10031</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>10057</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="C33" t="str">
         <f>"'"&amp;B33&amp;A33&amp;"'"&amp;","</f>
-        <v>'Nadie te ama como Yo10031',</v>
-      </c>
-      <c r="D33" s="1" t="str">
+        <v>'Misericordia Señor por tu Bondad10057',</v>
+      </c>
+      <c r="D33" s="8" t="str">
         <f>B33&amp;A33</f>
-        <v>Nadie te ama como Yo10031</v>
+        <v>Misericordia Señor por tu Bondad10057</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>10015</v>
+        <v>10031</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C34" t="str">
         <f>"'"&amp;B34&amp;A34&amp;"'"&amp;","</f>
-        <v>'Ofrenda de Amor10015',</v>
+        <v>'Nadie te ama como Yo10031',</v>
       </c>
       <c r="D34" s="1" t="str">
         <f>B34&amp;A34</f>
-        <v>Ofrenda de Amor10015</v>
+        <v>Nadie te ama como Yo10031</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>10033</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
+        <v>10015</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C35" t="str">
         <f>"'"&amp;B35&amp;A35&amp;"'"&amp;","</f>
-        <v>'Pacto de esperanza10033',</v>
+        <v>'Ofrenda de Amor10015',</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>B35&amp;A35</f>
-        <v>Pacto de esperanza10033</v>
+        <v>Ofrenda de Amor10015</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>10016</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>22</v>
+        <v>10033</v>
+      </c>
+      <c r="B36" t="s">
+        <v>33</v>
       </c>
       <c r="C36" t="str">
         <f>"'"&amp;B36&amp;A36&amp;"'"&amp;","</f>
-        <v>'Padre Nuestro10016',</v>
+        <v>'Pacto de esperanza10033',</v>
       </c>
       <c r="D36" s="1" t="str">
         <f>B36&amp;A36</f>
-        <v>Padre Nuestro10016</v>
+        <v>Pacto de esperanza10033</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C37" t="str">
         <f>"'"&amp;B37&amp;A37&amp;"'"&amp;","</f>
-        <v>'Padre Nuestro Gallego10017',</v>
+        <v>'Padre Nuestro10016',</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>B37&amp;A37</f>
-        <v>Padre Nuestro Gallego10017</v>
+        <v>Padre Nuestro10016</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10049</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>47</v>
+        <v>10017</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C38" t="str">
         <f>"'"&amp;B38&amp;A38&amp;"'"&amp;","</f>
-        <v>'Pan de Vida10049',</v>
+        <v>'Padre Nuestro Gallego10017',</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>B38&amp;A38</f>
-        <v>Pan de Vida10049</v>
+        <v>Padre Nuestro Gallego10017</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10036</v>
-      </c>
-      <c r="B39" t="s">
-        <v>35</v>
+        <v>10049</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C39" t="str">
         <f>"'"&amp;B39&amp;A39&amp;"'"&amp;","</f>
-        <v>'Perdona a tu pueblo Señor10036',</v>
+        <v>'Pan de Vida10049',</v>
       </c>
       <c r="D39" s="1" t="str">
         <f>B39&amp;A39</f>
-        <v>Perdona a tu pueblo Señor10036</v>
+        <v>Pan de Vida10049</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>10018</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>16</v>
+        <v>10036</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
       </c>
       <c r="C40" t="str">
         <f>"'"&amp;B40&amp;A40&amp;"'"&amp;","</f>
-        <v>'Pescador de Hombres10018',</v>
+        <v>'Perdona a tu pueblo Señor10036',</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>B40&amp;A40</f>
-        <v>Pescador de Hombres10018</v>
+        <v>Perdona a tu pueblo Señor10036</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>10026</v>
-      </c>
-      <c r="B41" t="s">
-        <v>26</v>
+        <v>10018</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C41" t="str">
         <f>"'"&amp;B41&amp;A41&amp;"'"&amp;","</f>
-        <v>'Por la vía dolorosa10026',</v>
+        <v>'Pescador de Hombres10018',</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>B41&amp;A41</f>
-        <v>Por la vía dolorosa10026</v>
+        <v>Pescador de Hombres10018</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10019</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
+        <v>10026</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
       </c>
       <c r="C42" t="str">
         <f>"'"&amp;B42&amp;A42&amp;"'"&amp;","</f>
-        <v>'Querido Padre10019',</v>
+        <v>'Por la vía dolorosa10026',</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>B42&amp;A42</f>
-        <v>Querido Padre10019</v>
+        <v>Por la vía dolorosa10026</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10047</v>
-      </c>
-      <c r="B43" t="s">
-        <v>141</v>
+        <v>10019</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C43" t="str">
         <f>"'"&amp;B43&amp;A43&amp;"'"&amp;","</f>
-        <v>'Recibe oh Padre Santo10047',</v>
+        <v>'Querido Padre10019',</v>
       </c>
       <c r="D43" s="1" t="str">
         <f>B43&amp;A43</f>
-        <v>Recibe oh Padre Santo10047</v>
+        <v>Querido Padre10019</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10037</v>
+        <v>10047</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="C44" t="str">
         <f>"'"&amp;B44&amp;A44&amp;"'"&amp;","</f>
-        <v>'Sagrado corazón10037',</v>
+        <v>'Recibe oh Padre Santo10047',</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>B44&amp;A44</f>
-        <v>Sagrado corazón10037</v>
+        <v>Recibe oh Padre Santo10047</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10025</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>25</v>
+        <v>10037</v>
+      </c>
+      <c r="B45" t="s">
+        <v>37</v>
       </c>
       <c r="C45" t="str">
         <f>"'"&amp;B45&amp;A45&amp;"'"&amp;","</f>
-        <v>'Saliendo del Pretorio10025',</v>
+        <v>'Sagrado corazón10037',</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>B45&amp;A45</f>
-        <v>Saliendo del Pretorio10025</v>
+        <v>Sagrado corazón10037</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10055</v>
-      </c>
-      <c r="B46" t="s">
-        <v>146</v>
+        <v>10025</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C46" t="str">
         <f>"'"&amp;B46&amp;A46&amp;"'"&amp;","</f>
-        <v>'Santo es el Señor mi Dios10055',</v>
+        <v>'Saliendo del Pretorio10025',</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>B46&amp;A46</f>
-        <v>Santo es el Señor mi Dios10055</v>
+        <v>Saliendo del Pretorio10025</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10039</v>
+        <v>10055</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C47" t="str">
         <f>"'"&amp;B47&amp;A47&amp;"'"&amp;","</f>
-        <v>'Señor ten piedad10039',</v>
+        <v>'Santo es el Señor mi Dios10055',</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>B47&amp;A47</f>
-        <v>Señor ten piedad10039</v>
+        <v>Santo es el Señor mi Dios10055</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10020</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>18</v>
+        <v>10039</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
       </c>
       <c r="C48" t="str">
         <f>"'"&amp;B48&amp;A48&amp;"'"&amp;","</f>
-        <v>'Somos ciudadanos de un mundo10020',</v>
+        <v>'Señor ten piedad10039',</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>B48&amp;A48</f>
-        <v>Somos ciudadanos de un mundo10020</v>
+        <v>Señor ten piedad10039</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>10046</v>
-      </c>
-      <c r="B49" t="s">
-        <v>85</v>
+        <v>10020</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C49" t="str">
         <f>"'"&amp;B49&amp;A49&amp;"'"&amp;","</f>
-        <v>'Te ofrezco Señor mi vida10046',</v>
+        <v>'Somos ciudadanos de un mundo10020',</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>B49&amp;A49</f>
-        <v>Te ofrezco Señor mi vida10046</v>
+        <v>Somos ciudadanos de un mundo10020</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>10021</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>19</v>
+        <v>10046</v>
+      </c>
+      <c r="B50" t="s">
+        <v>84</v>
       </c>
       <c r="C50" t="str">
         <f>"'"&amp;B50&amp;A50&amp;"'"&amp;","</f>
-        <v>'Te presentamos el vino y el pan10021',</v>
+        <v>'Te ofrezco Señor mi vida10046',</v>
       </c>
       <c r="D50" s="1" t="str">
         <f>B50&amp;A50</f>
-        <v>Te presentamos el vino y el pan10021</v>
+        <v>Te ofrezco Señor mi vida10046</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C51" t="str">
         <f>"'"&amp;B51&amp;A51&amp;"'"&amp;","</f>
-        <v>'Una Espiga10022',</v>
+        <v>'Te presentamos el vino y el pan10021',</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>B51&amp;A51</f>
-        <v>Una Espiga10022</v>
+        <v>Te presentamos el vino y el pan10021</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>10045</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>45</v>
+        <v>10022</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C52" t="str">
         <f>"'"&amp;B52&amp;A52&amp;"'"&amp;","</f>
-        <v>'Vamos cantando al Señor10045',</v>
+        <v>'Una Espiga10022',</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>B52&amp;A52</f>
-        <v>Vamos cantando al Señor10045</v>
+        <v>Una Espiga10022</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>10056</v>
-      </c>
-      <c r="B53" t="s">
-        <v>147</v>
+        <v>10045</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C53" t="str">
         <f>"'"&amp;B53&amp;A53&amp;"'"&amp;","</f>
-        <v>'Ven Señor a nuestra vida10056',</v>
+        <v>'Vamos cantando al Señor10045',</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>B53&amp;A53</f>
-        <v>Ven Señor a nuestra vida10056</v>
+        <v>Vamos cantando al Señor10045</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>10029</v>
+        <v>10056</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="C54" t="str">
         <f>"'"&amp;B54&amp;A54&amp;"'"&amp;","</f>
-        <v>'Venimos hoy a tu altar10029',</v>
+        <v>'Ven Señor a nuestra vida10056',</v>
       </c>
       <c r="D54" s="1" t="str">
         <f>B54&amp;A54</f>
-        <v>Venimos hoy a tu altar10029</v>
+        <v>Ven Señor a nuestra vida10056</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10027</v>
+        <v>10029</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C55" t="str">
         <f>"'"&amp;B55&amp;A55&amp;"'"&amp;","</f>
-        <v>'Vienen con alegría10027',</v>
+        <v>'Venimos hoy a tu altar10029',</v>
       </c>
       <c r="D55" s="1" t="str">
         <f>B55&amp;A55</f>
-        <v>Vienen con alegría10027</v>
+        <v>Venimos hoy a tu altar10029</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10023</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>3</v>
+        <v>10027</v>
+      </c>
+      <c r="B56" t="s">
+        <v>27</v>
       </c>
       <c r="C56" t="str">
         <f>"'"&amp;B56&amp;A56&amp;"'"&amp;","</f>
-        <v>'Ya no eres pan y vino10023',</v>
+        <v>'Vienen con alegría10027',</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>B56&amp;A56</f>
-        <v>Ya no eres pan y vino10023</v>
+        <v>Vienen con alegría10027</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10051</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>95</v>
+        <v>10023</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C57" t="str">
         <f>"'"&amp;B57&amp;A57&amp;"'"&amp;","</f>
-        <v>'Yo soy el Pan de la Vida10051',</v>
+        <v>'Ya no eres pan y vino10023',</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>B57&amp;A57</f>
-        <v>Yo soy el Pan de la Vida10051</v>
+        <v>Ya no eres pan y vino10023</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10057</v>
+        <v>10051</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C58" t="str">
         <f>"'"&amp;B58&amp;A58&amp;"'"&amp;","</f>
-        <v>'10057',</v>
+        <v>'Yo soy el Pan de la Vida10051',</v>
       </c>
       <c r="D58" s="1" t="str">
         <f>B58&amp;A58</f>
-        <v>10057</v>
+        <v>Yo soy el Pan de la Vida10051</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -2018,17 +2028,17 @@
       <c r="F70" s="3">
         <v>6</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>78</v>
+      <c r="G70" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>72</v>
       </c>
       <c r="I70" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J70" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2047,16 +2057,16 @@
         <v>7</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>72</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2064,16 +2074,16 @@
         <v>8</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>72</v>
       </c>
       <c r="I72" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J72" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2081,16 +2091,16 @@
         <v>9</v>
       </c>
       <c r="G73" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H73" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="I73" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J73" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2098,16 +2108,16 @@
         <v>10</v>
       </c>
       <c r="G74" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H74" s="3" t="s">
+      <c r="I74" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="J74" s="3" t="s">
         <v>90</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2118,13 +2128,13 @@
         <v>47</v>
       </c>
       <c r="H75" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="J75" s="3" t="s">
         <v>93</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2132,16 +2142,16 @@
         <v>12</v>
       </c>
       <c r="G76" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="I76" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2149,16 +2159,16 @@
         <v>13</v>
       </c>
       <c r="G77" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H77" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="I77" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2166,16 +2176,16 @@
         <v>14</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>72</v>
       </c>
       <c r="I78" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J78" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2183,16 +2193,16 @@
         <v>15</v>
       </c>
       <c r="G79" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H79" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="I79" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="J79" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -2200,16 +2210,16 @@
         <v>16</v>
       </c>
       <c r="G80" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H80" s="3" t="s">
+      <c r="I80" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J80" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="81" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2223,10 +2233,10 @@
         <v>72</v>
       </c>
       <c r="I81" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="82" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2240,10 +2250,10 @@
         <v>72</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="83" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2254,13 +2264,13 @@
         <v>50</v>
       </c>
       <c r="H83" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="84" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2268,16 +2278,16 @@
         <v>20</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>72</v>
       </c>
       <c r="I84" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J84" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="85" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2288,13 +2298,13 @@
         <v>51</v>
       </c>
       <c r="H85" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J85" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J85" s="3" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="86" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2305,13 +2315,13 @@
         <v>52</v>
       </c>
       <c r="H86" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I86" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="J86" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="J86" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="87" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2325,10 +2335,10 @@
         <v>72</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2336,16 +2346,16 @@
         <v>24</v>
       </c>
       <c r="G88" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="I88" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="J88" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="J88" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="89" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2359,10 +2369,10 @@
         <v>72</v>
       </c>
       <c r="I89" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J89" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="90" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2376,10 +2386,10 @@
         <v>67</v>
       </c>
       <c r="I90" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J90" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="J90" s="3" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="91" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2393,10 +2403,10 @@
         <v>72</v>
       </c>
       <c r="I91" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J91" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="92" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2410,10 +2420,10 @@
         <v>67</v>
       </c>
       <c r="I92" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J92" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="J92" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="93" spans="6:10" ht="30" x14ac:dyDescent="0.25">
@@ -2421,39 +2431,39 @@
         <v>29</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>72</v>
       </c>
       <c r="I93" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J93" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="J93" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="94" spans="6:10" x14ac:dyDescent="0.25">
       <c r="G94" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="6:10" x14ac:dyDescent="0.25">
       <c r="G95" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="6:10" x14ac:dyDescent="0.25">
       <c r="G96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:D71">
-    <sortCondition ref="B1:B71"/>
+    <sortCondition ref="B58:B71"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Canciones para Dios Word/Canciones_Dios_Lista_canciones.xlsx
+++ b/Canciones para Dios Word/Canciones_Dios_Lista_canciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterDev\Canciones para Dios Word\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DBE486-47A7-420D-8E6D-428403A42F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F7840F-E610-4AB1-8D3B-6DCFD5E69191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="148">
   <si>
     <t>A edificar la iglesia</t>
   </si>
@@ -541,7 +541,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -557,6 +557,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,591 +1207,594 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>10052</v>
-      </c>
-      <c r="B23" t="s">
-        <v>143</v>
+        <v>10058</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C23" t="str">
         <f>"'"&amp;B23&amp;A23&amp;"'"&amp;","</f>
-        <v>'Estoy a la puerta y llamo10052',</v>
+        <v>'El Señor es mi Pastor10058',</v>
       </c>
       <c r="D23" s="1" t="str">
         <f>B23&amp;A23</f>
-        <v>Estoy a la puerta y llamo10052</v>
+        <v>El Señor es mi Pastor10058</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>10010</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>2</v>
+        <v>10052</v>
+      </c>
+      <c r="B24" t="s">
+        <v>143</v>
       </c>
       <c r="C24" t="str">
         <f>"'"&amp;B24&amp;A24&amp;"'"&amp;","</f>
-        <v>'Granito de Mostaza10010',</v>
+        <v>'Estoy a la puerta y llamo10052',</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>B24&amp;A24</f>
-        <v>Granito de Mostaza10010</v>
+        <v>Estoy a la puerta y llamo10052</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>10041</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
+        <v>10010</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C25" t="str">
         <f>"'"&amp;B25&amp;A25&amp;"'"&amp;","</f>
-        <v>'Ha Traído la Esperanza10041',</v>
+        <v>'Granito de Mostaza10010',</v>
       </c>
       <c r="D25" s="1" t="str">
         <f>B25&amp;A25</f>
-        <v>Ha Traído la Esperanza10041</v>
+        <v>Granito de Mostaza10010</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>10011</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>10</v>
+        <v>10041</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
       </c>
       <c r="C26" t="str">
         <f>"'"&amp;B26&amp;A26&amp;"'"&amp;","</f>
-        <v>'Háblame Señor10011',</v>
+        <v>'Ha Traído la Esperanza10041',</v>
       </c>
       <c r="D26" s="1" t="str">
         <f>B26&amp;A26</f>
-        <v>Háblame Señor10011</v>
+        <v>Ha Traído la Esperanza10041</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>10053</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>137</v>
+        <v>10011</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C27" t="str">
         <f>"'"&amp;B27&amp;A27&amp;"'"&amp;","</f>
-        <v>'Hoy Señor te damos gracias10053',</v>
+        <v>'Háblame Señor10011',</v>
       </c>
       <c r="D27" s="1" t="str">
         <f>B27&amp;A27</f>
-        <v>Hoy Señor te damos gracias10053</v>
+        <v>Háblame Señor10011</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>10012</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>11</v>
+        <v>10053</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="C28" t="str">
         <f>"'"&amp;B28&amp;A28&amp;"'"&amp;","</f>
-        <v>'Junto a ti María10012',</v>
+        <v>'Hoy Señor te damos gracias10053',</v>
       </c>
       <c r="D28" s="1" t="str">
         <f>B28&amp;A28</f>
-        <v>Junto a ti María10012</v>
+        <v>Hoy Señor te damos gracias10053</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="str">
         <f>"'"&amp;B29&amp;A29&amp;"'"&amp;","</f>
-        <v>'Juntos como Hemanos10013',</v>
+        <v>'Junto a ti María10012',</v>
       </c>
       <c r="D29" s="1" t="str">
         <f>B29&amp;A29</f>
-        <v>Juntos como Hemanos10013</v>
+        <v>Junto a ti María10012</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>10054</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>144</v>
+        <v>10013</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C30" t="str">
         <f>"'"&amp;B30&amp;A30&amp;"'"&amp;","</f>
-        <v>'La bondad de Dios10054',</v>
+        <v>'Juntos como Hemanos10013',</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>B30&amp;A30</f>
-        <v>La bondad de Dios10054</v>
+        <v>Juntos como Hemanos10013</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>10014</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>13</v>
+        <v>10054</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="C31" t="str">
         <f>"'"&amp;B31&amp;A31&amp;"'"&amp;","</f>
-        <v>'La Paz esté con nosotros10014',</v>
+        <v>'La bondad de Dios10054',</v>
       </c>
       <c r="D31" s="1" t="str">
         <f>B31&amp;A31</f>
-        <v>La Paz esté con nosotros10014</v>
+        <v>La bondad de Dios10054</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>10032</v>
-      </c>
-      <c r="B32" t="s">
-        <v>32</v>
+        <v>10014</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C32" t="str">
         <f>"'"&amp;B32&amp;A32&amp;"'"&amp;","</f>
-        <v>'Milagro de amor10032',</v>
+        <v>'La Paz esté con nosotros10014',</v>
       </c>
       <c r="D32" s="1" t="str">
         <f>B32&amp;A32</f>
-        <v>Milagro de amor10032</v>
+        <v>La Paz esté con nosotros10014</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>10057</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>147</v>
+        <v>10032</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
       </c>
       <c r="C33" t="str">
         <f>"'"&amp;B33&amp;A33&amp;"'"&amp;","</f>
-        <v>'Misericordia Señor por tu Bondad10057',</v>
-      </c>
-      <c r="D33" s="8" t="str">
+        <v>'Milagro de amor10032',</v>
+      </c>
+      <c r="D33" s="1" t="str">
         <f>B33&amp;A33</f>
-        <v>Misericordia Señor por tu Bondad10057</v>
+        <v>Milagro de amor10032</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>10031</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>31</v>
+        <v>10057</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="C34" t="str">
         <f>"'"&amp;B34&amp;A34&amp;"'"&amp;","</f>
-        <v>'Nadie te ama como Yo10031',</v>
-      </c>
-      <c r="D34" s="1" t="str">
+        <v>'Misericordia Señor por tu Bondad10057',</v>
+      </c>
+      <c r="D34" s="8" t="str">
         <f>B34&amp;A34</f>
-        <v>Nadie te ama como Yo10031</v>
+        <v>Misericordia Señor por tu Bondad10057</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>10015</v>
+        <v>10031</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C35" t="str">
         <f>"'"&amp;B35&amp;A35&amp;"'"&amp;","</f>
-        <v>'Ofrenda de Amor10015',</v>
+        <v>'Nadie te ama como Yo10031',</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>B35&amp;A35</f>
-        <v>Ofrenda de Amor10015</v>
+        <v>Nadie te ama como Yo10031</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>10033</v>
-      </c>
-      <c r="B36" t="s">
-        <v>33</v>
+        <v>10015</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C36" t="str">
         <f>"'"&amp;B36&amp;A36&amp;"'"&amp;","</f>
-        <v>'Pacto de esperanza10033',</v>
+        <v>'Ofrenda de Amor10015',</v>
       </c>
       <c r="D36" s="1" t="str">
         <f>B36&amp;A36</f>
-        <v>Pacto de esperanza10033</v>
+        <v>Ofrenda de Amor10015</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>10016</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>22</v>
+        <v>10033</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
       </c>
       <c r="C37" t="str">
         <f>"'"&amp;B37&amp;A37&amp;"'"&amp;","</f>
-        <v>'Padre Nuestro10016',</v>
+        <v>'Pacto de esperanza10033',</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>B37&amp;A37</f>
-        <v>Padre Nuestro10016</v>
+        <v>Pacto de esperanza10033</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C38" t="str">
         <f>"'"&amp;B38&amp;A38&amp;"'"&amp;","</f>
-        <v>'Padre Nuestro Gallego10017',</v>
+        <v>'Padre Nuestro10016',</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>B38&amp;A38</f>
-        <v>Padre Nuestro Gallego10017</v>
+        <v>Padre Nuestro10016</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10049</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>47</v>
+        <v>10017</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C39" t="str">
         <f>"'"&amp;B39&amp;A39&amp;"'"&amp;","</f>
-        <v>'Pan de Vida10049',</v>
+        <v>'Padre Nuestro Gallego10017',</v>
       </c>
       <c r="D39" s="1" t="str">
         <f>B39&amp;A39</f>
-        <v>Pan de Vida10049</v>
+        <v>Padre Nuestro Gallego10017</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>10036</v>
-      </c>
-      <c r="B40" t="s">
-        <v>35</v>
+        <v>10049</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C40" t="str">
         <f>"'"&amp;B40&amp;A40&amp;"'"&amp;","</f>
-        <v>'Perdona a tu pueblo Señor10036',</v>
+        <v>'Pan de Vida10049',</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>B40&amp;A40</f>
-        <v>Perdona a tu pueblo Señor10036</v>
+        <v>Pan de Vida10049</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>10018</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
+        <v>10036</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
       </c>
       <c r="C41" t="str">
         <f>"'"&amp;B41&amp;A41&amp;"'"&amp;","</f>
-        <v>'Pescador de Hombres10018',</v>
+        <v>'Perdona a tu pueblo Señor10036',</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>B41&amp;A41</f>
-        <v>Pescador de Hombres10018</v>
+        <v>Perdona a tu pueblo Señor10036</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10026</v>
-      </c>
-      <c r="B42" t="s">
-        <v>26</v>
+        <v>10018</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C42" t="str">
         <f>"'"&amp;B42&amp;A42&amp;"'"&amp;","</f>
-        <v>'Por la vía dolorosa10026',</v>
+        <v>'Pescador de Hombres10018',</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>B42&amp;A42</f>
-        <v>Por la vía dolorosa10026</v>
+        <v>Pescador de Hombres10018</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10019</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>17</v>
+        <v>10026</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
       </c>
       <c r="C43" t="str">
         <f>"'"&amp;B43&amp;A43&amp;"'"&amp;","</f>
-        <v>'Querido Padre10019',</v>
+        <v>'Por la vía dolorosa10026',</v>
       </c>
       <c r="D43" s="1" t="str">
         <f>B43&amp;A43</f>
-        <v>Querido Padre10019</v>
+        <v>Por la vía dolorosa10026</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10047</v>
-      </c>
-      <c r="B44" t="s">
-        <v>140</v>
+        <v>10019</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C44" t="str">
         <f>"'"&amp;B44&amp;A44&amp;"'"&amp;","</f>
-        <v>'Recibe oh Padre Santo10047',</v>
+        <v>'Querido Padre10019',</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>B44&amp;A44</f>
-        <v>Recibe oh Padre Santo10047</v>
+        <v>Querido Padre10019</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10037</v>
+        <v>10047</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="C45" t="str">
         <f>"'"&amp;B45&amp;A45&amp;"'"&amp;","</f>
-        <v>'Sagrado corazón10037',</v>
+        <v>'Recibe oh Padre Santo10047',</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>B45&amp;A45</f>
-        <v>Sagrado corazón10037</v>
+        <v>Recibe oh Padre Santo10047</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10025</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>25</v>
+        <v>10037</v>
+      </c>
+      <c r="B46" t="s">
+        <v>37</v>
       </c>
       <c r="C46" t="str">
         <f>"'"&amp;B46&amp;A46&amp;"'"&amp;","</f>
-        <v>'Saliendo del Pretorio10025',</v>
+        <v>'Sagrado corazón10037',</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>B46&amp;A46</f>
-        <v>Saliendo del Pretorio10025</v>
+        <v>Sagrado corazón10037</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10055</v>
-      </c>
-      <c r="B47" t="s">
-        <v>145</v>
+        <v>10025</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C47" t="str">
         <f>"'"&amp;B47&amp;A47&amp;"'"&amp;","</f>
-        <v>'Santo es el Señor mi Dios10055',</v>
+        <v>'Saliendo del Pretorio10025',</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>B47&amp;A47</f>
-        <v>Santo es el Señor mi Dios10055</v>
+        <v>Saliendo del Pretorio10025</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10039</v>
+        <v>10055</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C48" t="str">
         <f>"'"&amp;B48&amp;A48&amp;"'"&amp;","</f>
-        <v>'Señor ten piedad10039',</v>
+        <v>'Santo es el Señor mi Dios10055',</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>B48&amp;A48</f>
-        <v>Señor ten piedad10039</v>
+        <v>Santo es el Señor mi Dios10055</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>10020</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>18</v>
+        <v>10039</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
       </c>
       <c r="C49" t="str">
         <f>"'"&amp;B49&amp;A49&amp;"'"&amp;","</f>
-        <v>'Somos ciudadanos de un mundo10020',</v>
+        <v>'Señor ten piedad10039',</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>B49&amp;A49</f>
-        <v>Somos ciudadanos de un mundo10020</v>
+        <v>Señor ten piedad10039</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>10046</v>
-      </c>
-      <c r="B50" t="s">
-        <v>84</v>
+        <v>10020</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C50" t="str">
         <f>"'"&amp;B50&amp;A50&amp;"'"&amp;","</f>
-        <v>'Te ofrezco Señor mi vida10046',</v>
+        <v>'Somos ciudadanos de un mundo10020',</v>
       </c>
       <c r="D50" s="1" t="str">
         <f>B50&amp;A50</f>
-        <v>Te ofrezco Señor mi vida10046</v>
+        <v>Somos ciudadanos de un mundo10020</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10021</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>19</v>
+        <v>10046</v>
+      </c>
+      <c r="B51" t="s">
+        <v>84</v>
       </c>
       <c r="C51" t="str">
         <f>"'"&amp;B51&amp;A51&amp;"'"&amp;","</f>
-        <v>'Te presentamos el vino y el pan10021',</v>
+        <v>'Te ofrezco Señor mi vida10046',</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>B51&amp;A51</f>
-        <v>Te presentamos el vino y el pan10021</v>
+        <v>Te ofrezco Señor mi vida10046</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C52" t="str">
         <f>"'"&amp;B52&amp;A52&amp;"'"&amp;","</f>
-        <v>'Una Espiga10022',</v>
+        <v>'Te presentamos el vino y el pan10021',</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>B52&amp;A52</f>
-        <v>Una Espiga10022</v>
+        <v>Te presentamos el vino y el pan10021</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>10045</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>45</v>
+        <v>10022</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C53" t="str">
         <f>"'"&amp;B53&amp;A53&amp;"'"&amp;","</f>
-        <v>'Vamos cantando al Señor10045',</v>
+        <v>'Una Espiga10022',</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>B53&amp;A53</f>
-        <v>Vamos cantando al Señor10045</v>
+        <v>Una Espiga10022</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>10056</v>
-      </c>
-      <c r="B54" t="s">
-        <v>146</v>
+        <v>10045</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C54" t="str">
         <f>"'"&amp;B54&amp;A54&amp;"'"&amp;","</f>
-        <v>'Ven Señor a nuestra vida10056',</v>
+        <v>'Vamos cantando al Señor10045',</v>
       </c>
       <c r="D54" s="1" t="str">
         <f>B54&amp;A54</f>
-        <v>Ven Señor a nuestra vida10056</v>
+        <v>Vamos cantando al Señor10045</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10029</v>
+        <v>10056</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="C55" t="str">
         <f>"'"&amp;B55&amp;A55&amp;"'"&amp;","</f>
-        <v>'Venimos hoy a tu altar10029',</v>
+        <v>'Ven Señor a nuestra vida10056',</v>
       </c>
       <c r="D55" s="1" t="str">
         <f>B55&amp;A55</f>
-        <v>Venimos hoy a tu altar10029</v>
+        <v>Ven Señor a nuestra vida10056</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10027</v>
+        <v>10029</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C56" t="str">
         <f>"'"&amp;B56&amp;A56&amp;"'"&amp;","</f>
-        <v>'Vienen con alegría10027',</v>
+        <v>'Venimos hoy a tu altar10029',</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>B56&amp;A56</f>
-        <v>Vienen con alegría10027</v>
+        <v>Venimos hoy a tu altar10029</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10023</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>3</v>
+        <v>10027</v>
+      </c>
+      <c r="B57" t="s">
+        <v>27</v>
       </c>
       <c r="C57" t="str">
         <f>"'"&amp;B57&amp;A57&amp;"'"&amp;","</f>
-        <v>'Ya no eres pan y vino10023',</v>
+        <v>'Vienen con alegría10027',</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>B57&amp;A57</f>
-        <v>Ya no eres pan y vino10023</v>
+        <v>Vienen con alegría10027</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10051</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>94</v>
+        <v>10023</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C58" t="str">
         <f>"'"&amp;B58&amp;A58&amp;"'"&amp;","</f>
-        <v>'Yo soy el Pan de la Vida10051',</v>
+        <v>'Ya no eres pan y vino10023',</v>
       </c>
       <c r="D58" s="1" t="str">
         <f>B58&amp;A58</f>
-        <v>Yo soy el Pan de la Vida10051</v>
+        <v>Ya no eres pan y vino10023</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10058</v>
+        <v>10051</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C59" t="str">
         <f>"'"&amp;B59&amp;A59&amp;"'"&amp;","</f>
-        <v>'10058',</v>
+        <v>'Yo soy el Pan de la Vida10051',</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>B59&amp;A59</f>
-        <v>10058</v>
+        <v>Yo soy el Pan de la Vida10051</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -1989,7 +1993,7 @@
       <c r="A69">
         <v>10068</v>
       </c>
-      <c r="C69" t="str">
+      <c r="C69" s="9" t="str">
         <f>"'"&amp;B69&amp;A69&amp;"'"&amp;","</f>
         <v>'10068',</v>
       </c>
@@ -2000,7 +2004,7 @@
       <c r="F69" s="3">
         <v>5</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="4" t="s">
         <v>46</v>
       </c>
       <c r="H69" s="3" t="s">
@@ -2463,7 +2467,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:D71">
-    <sortCondition ref="B58:B71"/>
+    <sortCondition ref="B1:B71"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Canciones para Dios Word/Canciones_Dios_Lista_canciones.xlsx
+++ b/Canciones para Dios Word/Canciones_Dios_Lista_canciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterDev\Canciones para Dios Word\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F7840F-E610-4AB1-8D3B-6DCFD5E69191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA04448-B3DE-4E4B-A5E5-1CA7A0913B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="149">
   <si>
     <t>A edificar la iglesia</t>
   </si>
@@ -480,6 +480,9 @@
   </si>
   <si>
     <t>Misericordia Señor por tu Bondad</t>
+  </si>
+  <si>
+    <t>Alma Misionera-Llévame donde los hombres…</t>
   </si>
 </sst>
 </file>
@@ -541,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -557,7 +560,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -842,9 +844,9 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.140625" customWidth="1"/>
     <col min="8" max="8" width="34.5703125" customWidth="1"/>
@@ -966,848 +968,851 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>10004</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>10059</v>
+      </c>
+      <c r="B8" t="s">
+        <v>148</v>
       </c>
       <c r="C8" t="str">
         <f>"'"&amp;B8&amp;A8&amp;"'"&amp;","</f>
-        <v>'Alto Escuchame10004',</v>
+        <v>'Alma Misionera-Llévame donde los hombres…10059',</v>
       </c>
       <c r="D8" s="1" t="str">
         <f>B8&amp;A8</f>
-        <v>Alto Escuchame10004</v>
+        <v>Alma Misionera-Llévame donde los hombres…10059</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>10035</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
+        <v>10004</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C9" t="str">
         <f>"'"&amp;B9&amp;A9&amp;"'"&amp;","</f>
-        <v>'Arrepiéntete y cree en el Evangelio10035',</v>
+        <v>'Alto Escuchame10004',</v>
       </c>
       <c r="D9" s="1" t="str">
         <f>B9&amp;A9</f>
-        <v>Arrepiéntete y cree en el Evangelio10035</v>
+        <v>Alto Escuchame10004</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>10050</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>116</v>
+        <v>10035</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
       </c>
       <c r="C10" t="str">
         <f>"'"&amp;B10&amp;A10&amp;"'"&amp;","</f>
-        <v>'Ave María10050',</v>
+        <v>'Arrepiéntete y cree en el Evangelio10035',</v>
       </c>
       <c r="D10" s="1" t="str">
         <f>B10&amp;A10</f>
-        <v>Ave María10050</v>
+        <v>Arrepiéntete y cree en el Evangelio10035</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10038</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
+        <v>10050</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C11" t="str">
         <f>"'"&amp;B11&amp;A11&amp;"'"&amp;","</f>
-        <v>'Bendito, bendito10038',</v>
+        <v>'Ave María10050',</v>
       </c>
       <c r="D11" s="1" t="str">
         <f>B11&amp;A11</f>
-        <v>Bendito, bendito10038</v>
+        <v>Ave María10050</v>
       </c>
       <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>10028</v>
+        <v>10038</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C12" t="str">
         <f>"'"&amp;B12&amp;A12&amp;"'"&amp;","</f>
-        <v>'Caminaré en presencia del Señor10028',</v>
+        <v>'Bendito, bendito10038',</v>
       </c>
       <c r="D12" s="1" t="str">
         <f>B12&amp;A12</f>
-        <v>Caminaré en presencia del Señor10028</v>
+        <v>Bendito, bendito10038</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>10043</v>
+        <v>10028</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C13" t="str">
         <f>"'"&amp;B13&amp;A13&amp;"'"&amp;","</f>
-        <v>'Cantemos al Amor de los Amores10043',</v>
+        <v>'Caminaré en presencia del Señor10028',</v>
       </c>
       <c r="D13" s="1" t="str">
         <f>B13&amp;A13</f>
-        <v>Cantemos al Amor de los Amores10043</v>
+        <v>Caminaré en presencia del Señor10028</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>10024</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>10043</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
       </c>
       <c r="C14" t="str">
         <f>"'"&amp;B14&amp;A14&amp;"'"&amp;","</f>
-        <v>'Con amor te presento Señor10024',</v>
+        <v>'Cantemos al Amor de los Amores10043',</v>
       </c>
       <c r="D14" s="1" t="str">
         <f>B14&amp;A14</f>
-        <v>Con amor te presento Señor10024</v>
+        <v>Cantemos al Amor de los Amores10043</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>10042</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
+        <v>10024</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C15" t="str">
         <f>"'"&amp;B15&amp;A15&amp;"'"&amp;","</f>
-        <v>'Cordero de Dios10042',</v>
+        <v>'Con amor te presento Señor10024',</v>
       </c>
       <c r="D15" s="1" t="str">
         <f>B15&amp;A15</f>
-        <v>Cordero de Dios10042</v>
+        <v>Con amor te presento Señor10024</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>10044</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>66</v>
+        <v>10042</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
       </c>
       <c r="C16" t="str">
         <f>"'"&amp;B16&amp;A16&amp;"'"&amp;","</f>
-        <v>'Cristo te necesita para amar10044',</v>
+        <v>'Cordero de Dios10042',</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>B16&amp;A16</f>
-        <v>Cristo te necesita para amar10044</v>
+        <v>Cordero de Dios10042</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>10007</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>10044</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="C17" t="str">
         <f>"'"&amp;B17&amp;A17&amp;"'"&amp;","</f>
-        <v>'Demos gracias al Señor10007',</v>
+        <v>'Cristo te necesita para amar10044',</v>
       </c>
       <c r="D17" s="1" t="str">
         <f>B17&amp;A17</f>
-        <v>Demos gracias al Señor10007</v>
+        <v>Cristo te necesita para amar10044</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>10034</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
+        <v>10007</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C18" t="str">
         <f>"'"&amp;B18&amp;A18&amp;"'"&amp;","</f>
-        <v>'Dichosos10034',</v>
+        <v>'Demos gracias al Señor10007',</v>
       </c>
       <c r="D18" s="1" t="str">
         <f>B18&amp;A18</f>
-        <v>Dichosos10034</v>
+        <v>Demos gracias al Señor10007</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>10008</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>10034</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
       </c>
       <c r="C19" t="str">
         <f>"'"&amp;B19&amp;A19&amp;"'"&amp;","</f>
-        <v>'Dios está aquí10008',</v>
+        <v>'Dichosos10034',</v>
       </c>
       <c r="D19" s="1" t="str">
         <f>B19&amp;A19</f>
-        <v>Dios está aquí10008</v>
+        <v>Dichosos10034</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>10040</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
+        <v>10008</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C20" t="str">
         <f>"'"&amp;B20&amp;A20&amp;"'"&amp;","</f>
-        <v>'Dios y hombre10040',</v>
+        <v>'Dios está aquí10008',</v>
       </c>
       <c r="D20" s="1" t="str">
         <f>B20&amp;A20</f>
-        <v>Dios y hombre10040</v>
+        <v>Dios está aquí10008</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>10030</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>10040</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
       </c>
       <c r="C21" t="str">
         <f>"'"&amp;B21&amp;A21&amp;"'"&amp;","</f>
-        <v>'El Alfarero - Vaso Nuevo10030',</v>
+        <v>'Dios y hombre10040',</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>B21&amp;A21</f>
-        <v>El Alfarero - Vaso Nuevo10030</v>
+        <v>Dios y hombre10040</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>10009</v>
+        <v>10030</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C22" t="str">
         <f>"'"&amp;B22&amp;A22&amp;"'"&amp;","</f>
-        <v>'El Diario de María10009',</v>
+        <v>'El Alfarero - Vaso Nuevo10030',</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>B22&amp;A22</f>
-        <v>El Diario de María10009</v>
+        <v>El Alfarero - Vaso Nuevo10030</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>10058</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>10009</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C23" t="str">
         <f>"'"&amp;B23&amp;A23&amp;"'"&amp;","</f>
-        <v>'El Señor es mi Pastor10058',</v>
+        <v>'El Diario de María10009',</v>
       </c>
       <c r="D23" s="1" t="str">
         <f>B23&amp;A23</f>
-        <v>El Señor es mi Pastor10058</v>
+        <v>El Diario de María10009</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>10052</v>
-      </c>
-      <c r="B24" t="s">
-        <v>143</v>
+        <v>10058</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="C24" t="str">
         <f>"'"&amp;B24&amp;A24&amp;"'"&amp;","</f>
-        <v>'Estoy a la puerta y llamo10052',</v>
+        <v>'El Señor es mi Pastor10058',</v>
       </c>
       <c r="D24" s="1" t="str">
         <f>B24&amp;A24</f>
-        <v>Estoy a la puerta y llamo10052</v>
+        <v>El Señor es mi Pastor10058</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>10010</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>2</v>
+        <v>10052</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
       </c>
       <c r="C25" t="str">
         <f>"'"&amp;B25&amp;A25&amp;"'"&amp;","</f>
-        <v>'Granito de Mostaza10010',</v>
+        <v>'Estoy a la puerta y llamo10052',</v>
       </c>
       <c r="D25" s="1" t="str">
         <f>B25&amp;A25</f>
-        <v>Granito de Mostaza10010</v>
+        <v>Estoy a la puerta y llamo10052</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>10041</v>
-      </c>
-      <c r="B26" t="s">
-        <v>41</v>
+        <v>10010</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C26" t="str">
         <f>"'"&amp;B26&amp;A26&amp;"'"&amp;","</f>
-        <v>'Ha Traído la Esperanza10041',</v>
+        <v>'Granito de Mostaza10010',</v>
       </c>
       <c r="D26" s="1" t="str">
         <f>B26&amp;A26</f>
-        <v>Ha Traído la Esperanza10041</v>
+        <v>Granito de Mostaza10010</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>10011</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>10041</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
       </c>
       <c r="C27" t="str">
         <f>"'"&amp;B27&amp;A27&amp;"'"&amp;","</f>
-        <v>'Háblame Señor10011',</v>
+        <v>'Ha Traído la Esperanza10041',</v>
       </c>
       <c r="D27" s="1" t="str">
         <f>B27&amp;A27</f>
-        <v>Háblame Señor10011</v>
+        <v>Ha Traído la Esperanza10041</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>10053</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>137</v>
+        <v>10011</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C28" t="str">
         <f>"'"&amp;B28&amp;A28&amp;"'"&amp;","</f>
-        <v>'Hoy Señor te damos gracias10053',</v>
+        <v>'Háblame Señor10011',</v>
       </c>
       <c r="D28" s="1" t="str">
         <f>B28&amp;A28</f>
-        <v>Hoy Señor te damos gracias10053</v>
+        <v>Háblame Señor10011</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>10012</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>11</v>
+        <v>10053</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="C29" t="str">
         <f>"'"&amp;B29&amp;A29&amp;"'"&amp;","</f>
-        <v>'Junto a ti María10012',</v>
+        <v>'Hoy Señor te damos gracias10053',</v>
       </c>
       <c r="D29" s="1" t="str">
         <f>B29&amp;A29</f>
-        <v>Junto a ti María10012</v>
+        <v>Hoy Señor te damos gracias10053</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" t="str">
         <f>"'"&amp;B30&amp;A30&amp;"'"&amp;","</f>
-        <v>'Juntos como Hemanos10013',</v>
+        <v>'Junto a ti María10012',</v>
       </c>
       <c r="D30" s="1" t="str">
         <f>B30&amp;A30</f>
-        <v>Juntos como Hemanos10013</v>
+        <v>Junto a ti María10012</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>10054</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>144</v>
+        <v>10013</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C31" t="str">
         <f>"'"&amp;B31&amp;A31&amp;"'"&amp;","</f>
-        <v>'La bondad de Dios10054',</v>
+        <v>'Juntos como Hemanos10013',</v>
       </c>
       <c r="D31" s="1" t="str">
         <f>B31&amp;A31</f>
-        <v>La bondad de Dios10054</v>
+        <v>Juntos como Hemanos10013</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>10014</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>13</v>
+        <v>10054</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="C32" t="str">
         <f>"'"&amp;B32&amp;A32&amp;"'"&amp;","</f>
-        <v>'La Paz esté con nosotros10014',</v>
+        <v>'La bondad de Dios10054',</v>
       </c>
       <c r="D32" s="1" t="str">
         <f>B32&amp;A32</f>
-        <v>La Paz esté con nosotros10014</v>
+        <v>La bondad de Dios10054</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>10032</v>
-      </c>
-      <c r="B33" t="s">
-        <v>32</v>
+        <v>10014</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C33" t="str">
         <f>"'"&amp;B33&amp;A33&amp;"'"&amp;","</f>
-        <v>'Milagro de amor10032',</v>
+        <v>'La Paz esté con nosotros10014',</v>
       </c>
       <c r="D33" s="1" t="str">
         <f>B33&amp;A33</f>
-        <v>Milagro de amor10032</v>
+        <v>La Paz esté con nosotros10014</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>10057</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>147</v>
+        <v>10032</v>
+      </c>
+      <c r="B34" t="s">
+        <v>32</v>
       </c>
       <c r="C34" t="str">
         <f>"'"&amp;B34&amp;A34&amp;"'"&amp;","</f>
-        <v>'Misericordia Señor por tu Bondad10057',</v>
-      </c>
-      <c r="D34" s="8" t="str">
+        <v>'Milagro de amor10032',</v>
+      </c>
+      <c r="D34" s="1" t="str">
         <f>B34&amp;A34</f>
-        <v>Misericordia Señor por tu Bondad10057</v>
+        <v>Milagro de amor10032</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>10031</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>31</v>
+        <v>10057</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>147</v>
       </c>
       <c r="C35" t="str">
         <f>"'"&amp;B35&amp;A35&amp;"'"&amp;","</f>
-        <v>'Nadie te ama como Yo10031',</v>
-      </c>
-      <c r="D35" s="1" t="str">
+        <v>'Misericordia Señor por tu Bondad10057',</v>
+      </c>
+      <c r="D35" s="8" t="str">
         <f>B35&amp;A35</f>
-        <v>Nadie te ama como Yo10031</v>
+        <v>Misericordia Señor por tu Bondad10057</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>10015</v>
+        <v>10031</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C36" t="str">
         <f>"'"&amp;B36&amp;A36&amp;"'"&amp;","</f>
-        <v>'Ofrenda de Amor10015',</v>
+        <v>'Nadie te ama como Yo10031',</v>
       </c>
       <c r="D36" s="1" t="str">
         <f>B36&amp;A36</f>
-        <v>Ofrenda de Amor10015</v>
+        <v>Nadie te ama como Yo10031</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>10033</v>
-      </c>
-      <c r="B37" t="s">
-        <v>33</v>
+        <v>10015</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C37" t="str">
         <f>"'"&amp;B37&amp;A37&amp;"'"&amp;","</f>
-        <v>'Pacto de esperanza10033',</v>
+        <v>'Ofrenda de Amor10015',</v>
       </c>
       <c r="D37" s="1" t="str">
         <f>B37&amp;A37</f>
-        <v>Pacto de esperanza10033</v>
+        <v>Ofrenda de Amor10015</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>10016</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>22</v>
+        <v>10033</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
       </c>
       <c r="C38" t="str">
         <f>"'"&amp;B38&amp;A38&amp;"'"&amp;","</f>
-        <v>'Padre Nuestro10016',</v>
+        <v>'Pacto de esperanza10033',</v>
       </c>
       <c r="D38" s="1" t="str">
         <f>B38&amp;A38</f>
-        <v>Padre Nuestro10016</v>
+        <v>Pacto de esperanza10033</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C39" t="str">
         <f>"'"&amp;B39&amp;A39&amp;"'"&amp;","</f>
-        <v>'Padre Nuestro Gallego10017',</v>
+        <v>'Padre Nuestro10016',</v>
       </c>
       <c r="D39" s="1" t="str">
         <f>B39&amp;A39</f>
-        <v>Padre Nuestro Gallego10017</v>
+        <v>Padre Nuestro10016</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>10049</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>47</v>
+        <v>10017</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C40" t="str">
         <f>"'"&amp;B40&amp;A40&amp;"'"&amp;","</f>
-        <v>'Pan de Vida10049',</v>
+        <v>'Padre Nuestro Gallego10017',</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>B40&amp;A40</f>
-        <v>Pan de Vida10049</v>
+        <v>Padre Nuestro Gallego10017</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>10036</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
+        <v>10049</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="C41" t="str">
         <f>"'"&amp;B41&amp;A41&amp;"'"&amp;","</f>
-        <v>'Perdona a tu pueblo Señor10036',</v>
+        <v>'Pan de Vida10049',</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>B41&amp;A41</f>
-        <v>Perdona a tu pueblo Señor10036</v>
+        <v>Pan de Vida10049</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>10018</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>16</v>
+        <v>10036</v>
+      </c>
+      <c r="B42" t="s">
+        <v>35</v>
       </c>
       <c r="C42" t="str">
         <f>"'"&amp;B42&amp;A42&amp;"'"&amp;","</f>
-        <v>'Pescador de Hombres10018',</v>
+        <v>'Perdona a tu pueblo Señor10036',</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>B42&amp;A42</f>
-        <v>Pescador de Hombres10018</v>
+        <v>Perdona a tu pueblo Señor10036</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>10026</v>
-      </c>
-      <c r="B43" t="s">
-        <v>26</v>
+        <v>10018</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C43" t="str">
         <f>"'"&amp;B43&amp;A43&amp;"'"&amp;","</f>
-        <v>'Por la vía dolorosa10026',</v>
+        <v>'Pescador de Hombres10018',</v>
       </c>
       <c r="D43" s="1" t="str">
         <f>B43&amp;A43</f>
-        <v>Por la vía dolorosa10026</v>
+        <v>Pescador de Hombres10018</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>10019</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>17</v>
+        <v>10026</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
       </c>
       <c r="C44" t="str">
         <f>"'"&amp;B44&amp;A44&amp;"'"&amp;","</f>
-        <v>'Querido Padre10019',</v>
+        <v>'Por la vía dolorosa10026',</v>
       </c>
       <c r="D44" s="1" t="str">
         <f>B44&amp;A44</f>
-        <v>Querido Padre10019</v>
+        <v>Por la vía dolorosa10026</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>10047</v>
-      </c>
-      <c r="B45" t="s">
-        <v>140</v>
+        <v>10019</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C45" t="str">
         <f>"'"&amp;B45&amp;A45&amp;"'"&amp;","</f>
-        <v>'Recibe oh Padre Santo10047',</v>
+        <v>'Querido Padre10019',</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>B45&amp;A45</f>
-        <v>Recibe oh Padre Santo10047</v>
+        <v>Querido Padre10019</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>10037</v>
+        <v>10047</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="C46" t="str">
         <f>"'"&amp;B46&amp;A46&amp;"'"&amp;","</f>
-        <v>'Sagrado corazón10037',</v>
+        <v>'Recibe oh Padre Santo10047',</v>
       </c>
       <c r="D46" s="1" t="str">
         <f>B46&amp;A46</f>
-        <v>Sagrado corazón10037</v>
+        <v>Recibe oh Padre Santo10047</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>10025</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>25</v>
+        <v>10037</v>
+      </c>
+      <c r="B47" t="s">
+        <v>37</v>
       </c>
       <c r="C47" t="str">
         <f>"'"&amp;B47&amp;A47&amp;"'"&amp;","</f>
-        <v>'Saliendo del Pretorio10025',</v>
+        <v>'Sagrado corazón10037',</v>
       </c>
       <c r="D47" s="1" t="str">
         <f>B47&amp;A47</f>
-        <v>Saliendo del Pretorio10025</v>
+        <v>Sagrado corazón10037</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>10055</v>
-      </c>
-      <c r="B48" t="s">
-        <v>145</v>
+        <v>10025</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C48" t="str">
         <f>"'"&amp;B48&amp;A48&amp;"'"&amp;","</f>
-        <v>'Santo es el Señor mi Dios10055',</v>
+        <v>'Saliendo del Pretorio10025',</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>B48&amp;A48</f>
-        <v>Santo es el Señor mi Dios10055</v>
+        <v>Saliendo del Pretorio10025</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>10039</v>
+        <v>10055</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C49" t="str">
         <f>"'"&amp;B49&amp;A49&amp;"'"&amp;","</f>
-        <v>'Señor ten piedad10039',</v>
+        <v>'Santo es el Señor mi Dios10055',</v>
       </c>
       <c r="D49" s="1" t="str">
         <f>B49&amp;A49</f>
-        <v>Señor ten piedad10039</v>
+        <v>Santo es el Señor mi Dios10055</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>10020</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>18</v>
+        <v>10039</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
       </c>
       <c r="C50" t="str">
         <f>"'"&amp;B50&amp;A50&amp;"'"&amp;","</f>
-        <v>'Somos ciudadanos de un mundo10020',</v>
+        <v>'Señor ten piedad10039',</v>
       </c>
       <c r="D50" s="1" t="str">
         <f>B50&amp;A50</f>
-        <v>Somos ciudadanos de un mundo10020</v>
+        <v>Señor ten piedad10039</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>10046</v>
-      </c>
-      <c r="B51" t="s">
-        <v>84</v>
+        <v>10020</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C51" t="str">
         <f>"'"&amp;B51&amp;A51&amp;"'"&amp;","</f>
-        <v>'Te ofrezco Señor mi vida10046',</v>
+        <v>'Somos ciudadanos de un mundo10020',</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>B51&amp;A51</f>
-        <v>Te ofrezco Señor mi vida10046</v>
+        <v>Somos ciudadanos de un mundo10020</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>10021</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>19</v>
+        <v>10046</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
       </c>
       <c r="C52" t="str">
         <f>"'"&amp;B52&amp;A52&amp;"'"&amp;","</f>
-        <v>'Te presentamos el vino y el pan10021',</v>
+        <v>'Te ofrezco Señor mi vida10046',</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>B52&amp;A52</f>
-        <v>Te presentamos el vino y el pan10021</v>
+        <v>Te ofrezco Señor mi vida10046</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C53" t="str">
         <f>"'"&amp;B53&amp;A53&amp;"'"&amp;","</f>
-        <v>'Una Espiga10022',</v>
+        <v>'Te presentamos el vino y el pan10021',</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>B53&amp;A53</f>
-        <v>Una Espiga10022</v>
+        <v>Te presentamos el vino y el pan10021</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>10045</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>45</v>
+        <v>10022</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C54" t="str">
         <f>"'"&amp;B54&amp;A54&amp;"'"&amp;","</f>
-        <v>'Vamos cantando al Señor10045',</v>
+        <v>'Una Espiga10022',</v>
       </c>
       <c r="D54" s="1" t="str">
         <f>B54&amp;A54</f>
-        <v>Vamos cantando al Señor10045</v>
+        <v>Una Espiga10022</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>10056</v>
-      </c>
-      <c r="B55" t="s">
-        <v>146</v>
+        <v>10045</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="C55" t="str">
         <f>"'"&amp;B55&amp;A55&amp;"'"&amp;","</f>
-        <v>'Ven Señor a nuestra vida10056',</v>
+        <v>'Vamos cantando al Señor10045',</v>
       </c>
       <c r="D55" s="1" t="str">
         <f>B55&amp;A55</f>
-        <v>Ven Señor a nuestra vida10056</v>
+        <v>Vamos cantando al Señor10045</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>10029</v>
+        <v>10056</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="C56" t="str">
         <f>"'"&amp;B56&amp;A56&amp;"'"&amp;","</f>
-        <v>'Venimos hoy a tu altar10029',</v>
+        <v>'Ven Señor a nuestra vida10056',</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>B56&amp;A56</f>
-        <v>Venimos hoy a tu altar10029</v>
+        <v>Ven Señor a nuestra vida10056</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>10027</v>
+        <v>10029</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C57" t="str">
         <f>"'"&amp;B57&amp;A57&amp;"'"&amp;","</f>
-        <v>'Vienen con alegría10027',</v>
+        <v>'Venimos hoy a tu altar10029',</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>B57&amp;A57</f>
-        <v>Vienen con alegría10027</v>
+        <v>Venimos hoy a tu altar10029</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>10023</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>3</v>
+        <v>10027</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
       </c>
       <c r="C58" t="str">
         <f>"'"&amp;B58&amp;A58&amp;"'"&amp;","</f>
-        <v>'Ya no eres pan y vino10023',</v>
+        <v>'Vienen con alegría10027',</v>
       </c>
       <c r="D58" s="1" t="str">
         <f>B58&amp;A58</f>
-        <v>Ya no eres pan y vino10023</v>
+        <v>Vienen con alegría10027</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>10051</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>94</v>
+        <v>10023</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C59" t="str">
         <f>"'"&amp;B59&amp;A59&amp;"'"&amp;","</f>
-        <v>'Yo soy el Pan de la Vida10051',</v>
+        <v>'Ya no eres pan y vino10023',</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>B59&amp;A59</f>
-        <v>Yo soy el Pan de la Vida10051</v>
+        <v>Ya no eres pan y vino10023</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>10059</v>
+        <v>10051</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="C60" t="str">
         <f>"'"&amp;B60&amp;A60&amp;"'"&amp;","</f>
-        <v>'10059',</v>
+        <v>'Yo soy el Pan de la Vida10051',</v>
       </c>
       <c r="D60" s="1" t="str">
         <f>B60&amp;A60</f>
-        <v>10059</v>
+        <v>Yo soy el Pan de la Vida10051</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -1993,7 +1998,7 @@
       <c r="A69">
         <v>10068</v>
       </c>
-      <c r="C69" s="9" t="str">
+      <c r="C69" t="str">
         <f>"'"&amp;B69&amp;A69&amp;"'"&amp;","</f>
         <v>'10068',</v>
       </c>
@@ -2467,7 +2472,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:D71">
-    <sortCondition ref="B1:B71"/>
+    <sortCondition ref="B60:B71"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
